--- a/docs/Files/ODYM_Tutorial6_EoLRecoveryRate_V1.0_EVLIB.xlsx
+++ b/docs/Files/ODYM_Tutorial6_EoLRecoveryRate_V1.0_EVLIB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D56AFCB-BD57-496C-B942-1F6C3A6CC26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F728B7A-61C2-4D2B-8E39-23AA0BDB4DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,9 +335,6 @@
     <t>Lanphear</t>
   </si>
   <si>
-    <t>ODYM_Classifications_Master_EV_LIB</t>
-  </si>
-  <si>
     <t>EV LIB</t>
   </si>
   <si>
@@ -354,6 +351,9 @@
   </si>
   <si>
     <t>Other scrap</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EV_LIB</t>
   </si>
 </sst>
 </file>
@@ -975,7 +975,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1206,13 +1206,16 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="E2">
+        <v>0.85</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1229,13 +1232,16 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E3">
+        <v>0.9</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1252,13 +1258,16 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>109</v>
+      <c r="E4">
+        <v>0.85</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1275,13 +1284,16 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E5">
+        <v>0.6</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1298,13 +1310,16 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="C6" t="s">
-        <v>107</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="E6">
+        <v>0.95</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1321,13 +1336,16 @@
         <v>59</v>
       </c>
       <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E7">
+        <v>0.95</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1344,13 +1362,16 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>109</v>
+      <c r="E8">
+        <v>0.9</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1367,13 +1388,16 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E9">
+        <v>0.75</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1390,13 +1414,16 @@
         <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="E10">
+        <v>0.84107142857142903</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1413,13 +1440,16 @@
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E11">
+        <v>0.84047619047619104</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1436,13 +1466,16 @@
         <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>109</v>
+      <c r="E12">
+        <v>0.83988095238095295</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1459,13 +1492,16 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E13">
+        <v>0.83928571428571397</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1482,13 +1518,16 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" t="s">
         <v>106</v>
       </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="E14">
+        <v>0.83869047619047599</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1505,13 +1544,16 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="s">
         <v>106</v>
       </c>
-      <c r="C15" t="s">
-        <v>107</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E15">
+        <v>0.838095238095238</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1528,13 +1570,16 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>109</v>
+      <c r="E16">
+        <v>0.83750000000000002</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1551,13 +1596,16 @@
         <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="E17">
+        <v>0.83690476190476204</v>
       </c>
       <c r="F17">
         <v>1</v>
